--- a/docs/design/api-spec.xlsx
+++ b/docs/design/api-spec.xlsx
@@ -599,7 +599,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>· design.md §5(서비스)·기능 정의에서 파생. 2026-07-19 기준(백엔드 실 라우트 + 프론트 실 호출 대조).</t>
+          <t>· design.md §5(서비스)·기능 정의에서 파생. 2026-07-20 기준(백엔드 실 라우트 + 프론트 실 호출 대조 + 라이브 재검증).</t>
         </is>
       </c>
     </row>
@@ -627,14 +627,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>· 상태: ✅ 구현·연동 · 🔷 백엔드만 · 🟡 프론트 mock · ⚪ 미착수 · ⏸ 보류/미기동.</t>
+          <t>· 상태: ✅ 구현·연동 · 🔷 백엔드만/미호출 · 🟡 프론트 mock · ⚪ 미착수 · ⏸ 보류.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>· 총 64행(엔드포인트) / 실 배포 서비스 8 + 스테이징 1(ocr) + 게이트웨이 + ML서빙.</t>
+          <t>· 총 64행(번호 63 + 무번호 google OAuth) / 실 배포 앱서비스 9(ocr 포함) + 게이트웨이 + ML서빙.</t>
         </is>
       </c>
     </row>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>⏸ 미기동</t>
+          <t>✅ (실배포·기동)</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="K62" s="6" t="inlineStr">
         <is>
-          <t>⏸ 미기동</t>
+          <t>✅ (실배포·기동)</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>⚪</t>
+          <t>🔷 (serving 실행·mealplan flag off)</t>
         </is>
       </c>
     </row>
